--- a/data/trans_orig/Q20C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q20C-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio, en meses, que estuvieron en la lista de espera antes de la hospitalización</t>
+          <t>Tiempo medio, en meses, que estuvieron en la lista de espera antes de la hospitalización (tasa de respuesta: 95,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 10,03</t>
+          <t>0,73; 10,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 11,49</t>
+          <t>2,47; 11,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 8,0</t>
+          <t>0,47; 8,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 8,8</t>
+          <t>2,78; 9,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,13; 16,12</t>
+          <t>4,13; 16,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,12 +856,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,59</t>
+          <t>1,7; 5,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,33</t>
+          <t>2,0; 6,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 8,48</t>
+          <t>1,7; 8,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 7,71</t>
+          <t>2,61; 7,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -896,17 +896,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,18</t>
+          <t>2,09; 6,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,66</t>
+          <t>2,7; 6,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 9,33</t>
+          <t>3,3; 9,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,85</t>
+          <t>1,48; 4,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 8,18</t>
+          <t>2,17; 8,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,19</t>
+          <t>1,37; 4,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 28,5</t>
+          <t>1,15; 28,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 7,66</t>
+          <t>1,43; 7,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 9,64</t>
+          <t>4,66; 10,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 11,43</t>
+          <t>4,37; 11,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 25,52</t>
+          <t>3,69; 24,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,59</t>
+          <t>2,09; 5,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 8,0</t>
+          <t>3,87; 7,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 7,18</t>
+          <t>3,04; 7,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 20,65</t>
+          <t>3,79; 19,75</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 20,99</t>
+          <t>7,68; 20,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 15,28</t>
+          <t>4,41; 15,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 21,99</t>
+          <t>5,49; 21,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 19,16</t>
+          <t>3,91; 16,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 12,28</t>
+          <t>3,58; 12,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 9,93</t>
+          <t>4,63; 10,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 8,99</t>
+          <t>4,26; 9,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,36</t>
+          <t>2,26; 4,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 13,59</t>
+          <t>5,18; 12,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,47; 10,54</t>
+          <t>5,35; 10,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,92; 13,66</t>
+          <t>5,97; 14,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 10,77</t>
+          <t>3,67; 10,62</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 14,32</t>
+          <t>3,53; 15,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,01</t>
+          <t>1,67; 7,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,98</t>
+          <t>3,72; 8,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,82; 9,55</t>
+          <t>2,97; 10,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,9</t>
+          <t>2,38; 5,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,41</t>
+          <t>2,08; 4,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,72; 13,69</t>
+          <t>4,07; 14,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 10,03</t>
+          <t>3,76; 10,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 8,56</t>
+          <t>3,54; 8,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,08</t>
+          <t>2,28; 5,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 9,78</t>
+          <t>4,47; 9,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,82; 8,63</t>
+          <t>3,95; 8,79</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,94; 45,88</t>
+          <t>5,86; 44,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,62; 16,22</t>
+          <t>3,72; 15,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,01; 52,24</t>
+          <t>3,73; 56,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,21; 14,87</t>
+          <t>5,13; 14,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,29; 7,21</t>
+          <t>3,35; 7,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,88; 10,72</t>
+          <t>1,96; 10,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,73; 12,99</t>
+          <t>4,16; 13,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,71; 18,8</t>
+          <t>4,8; 18,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,17; 22,04</t>
+          <t>4,98; 20,54</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,51; 10,26</t>
+          <t>3,67; 10,63</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,36; 29,93</t>
+          <t>5,48; 31,06</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,15; 14,26</t>
+          <t>6,15; 14,53</t>
         </is>
       </c>
     </row>
@@ -1561,17 +1561,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,37</t>
+          <t>0,79; 5,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,16; 13,26</t>
+          <t>3,0; 13,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,41</t>
+          <t>1,53; 4,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1581,37 +1581,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,86</t>
+          <t>1,13; 3,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,99</t>
+          <t>1,45; 4,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,92; 8,03</t>
+          <t>2,99; 8,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 8,09</t>
+          <t>1,2; 8,1</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,34</t>
+          <t>1,44; 4,32</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,45</t>
+          <t>2,35; 6,67</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,85; 6,41</t>
+          <t>2,84; 6,33</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,95; 12,93</t>
+          <t>4,97; 11,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,47</t>
+          <t>4,05; 7,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,69; 14,64</t>
+          <t>5,52; 13,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,2; 10,62</t>
+          <t>5,24; 10,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,98</t>
+          <t>3,43; 5,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,96</t>
+          <t>4,43; 6,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,18</t>
+          <t>4,89; 7,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,32; 9,23</t>
+          <t>4,39; 9,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,61</t>
+          <t>4,39; 7,92</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,76</t>
+          <t>4,52; 6,61</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,71; 9,91</t>
+          <t>5,83; 10,25</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,54</t>
+          <t>5,18; 8,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q20C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q20C-Edad-trans_orig.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 10,03</t>
+          <t>0,47; 10,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 8,0</t>
+          <t>0,46; 8,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 9,4</t>
+          <t>2,59; 9,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,13; 16,16</t>
+          <t>4,48; 16,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,96</t>
+          <t>6,6</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,37</t>
+          <t>2,34</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>4,75</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,75</t>
+          <t>1,47; 5,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -876,17 +876,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 8,78</t>
+          <t>1,69; 8,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 7,67</t>
+          <t>2,61; 7,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 10,54</t>
+          <t>3,05; 11,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -896,22 +896,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,1</t>
+          <t>2,21; 6,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,0</t>
+          <t>2,61; 5,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 9,61</t>
+          <t>3,16; 9,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 10,01</t>
+          <t>1,0; 9,8</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,64</t>
+          <t>9,29</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,89</t>
+          <t>9,35</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,17</t>
+          <t>9,33</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,63</t>
+          <t>1,65; 4,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,28</t>
+          <t>2,16; 7,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,22</t>
+          <t>1,27; 4,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 28,48</t>
+          <t>1,4; 27,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 7,79</t>
+          <t>1,57; 7,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 10,18</t>
+          <t>4,61; 10,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,37; 11,31</t>
+          <t>4,27; 11,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 24,47</t>
+          <t>3,87; 24,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,36</t>
+          <t>2,0; 5,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 7,77</t>
+          <t>4,03; 7,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,07</t>
+          <t>3,01; 7,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 19,75</t>
+          <t>3,94; 19,14</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,74</t>
+          <t>9,64</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,2</t>
+          <t>4,22</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,66</t>
+          <t>7,27</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,68; 20,99</t>
+          <t>6,43; 21,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 15,73</t>
+          <t>4,38; 15,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 21,08</t>
+          <t>5,43; 21,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 16,92</t>
+          <t>5,31; 17,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 12,68</t>
+          <t>3,43; 13,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 10,16</t>
+          <t>4,69; 10,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 9,01</t>
+          <t>4,51; 9,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,3</t>
+          <t>2,92; 6,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 12,72</t>
+          <t>4,89; 12,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 10,48</t>
+          <t>5,37; 10,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 14,69</t>
+          <t>5,98; 14,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 10,62</t>
+          <t>4,65; 11,98</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,42</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,45</t>
+          <t>6,94</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>5,92</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 15,05</t>
+          <t>3,22; 13,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,25</t>
+          <t>1,76; 6,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,72; 8,19</t>
+          <t>3,66; 8,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 10,1</t>
+          <t>2,8; 9,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,82</t>
+          <t>2,46; 5,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,38</t>
+          <t>2,07; 4,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 14,56</t>
+          <t>3,98; 14,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 10,66</t>
+          <t>4,06; 11,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 8,79</t>
+          <t>3,47; 9,19</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,06</t>
+          <t>2,34; 4,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 9,88</t>
+          <t>4,4; 9,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,79</t>
+          <t>3,73; 8,46</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,73</t>
+          <t>8,5</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,81</t>
+          <t>8,04</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,75</t>
+          <t>8,37</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,86; 44,8</t>
+          <t>5,6; 45,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,72; 15,97</t>
+          <t>3,74; 15,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,73; 56,47</t>
+          <t>4,01; 45,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,13; 14,87</t>
+          <t>5,22; 15,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,35; 7,15</t>
+          <t>3,21; 7,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,96; 10,65</t>
+          <t>1,82; 10,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,16; 13,71</t>
+          <t>3,86; 13,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,8; 18,48</t>
+          <t>4,58; 17,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,98; 20,54</t>
+          <t>5,04; 19,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,67; 10,63</t>
+          <t>3,53; 10,4</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,48; 31,06</t>
+          <t>5,43; 30,34</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,15; 14,53</t>
+          <t>5,6; 13,05</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>4,67</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,12</t>
+          <t>4,08</t>
         </is>
       </c>
     </row>
@@ -1561,57 +1561,57 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,48</t>
+          <t>0,98; 5,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,0; 13,26</t>
+          <t>3,13; 14,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,4</t>
+          <t>1,68; 4,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,8</t>
+          <t>1,0; 9,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,88</t>
+          <t>1,13; 4,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,87</t>
+          <t>1,52; 5,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 8,28</t>
+          <t>2,91; 7,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 8,1</t>
+          <t>1,12; 7,16</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,32</t>
+          <t>1,37; 4,28</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,67</t>
+          <t>2,49; 6,76</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 6,33</t>
+          <t>2,8; 6,2</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>7,48</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,9</t>
+          <t>6,05</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,61</t>
+          <t>6,84</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,97; 11,96</t>
+          <t>4,87; 12,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,61</t>
+          <t>4,02; 7,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,52; 13,84</t>
+          <t>5,33; 14,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,24; 10,0</t>
+          <t>5,57; 10,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,95</t>
+          <t>3,41; 6,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,99</t>
+          <t>4,41; 6,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,89; 7,87</t>
+          <t>4,92; 8,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,39; 9,14</t>
+          <t>4,51; 8,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,92</t>
+          <t>4,36; 7,7</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,61</t>
+          <t>4,61; 6,61</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,83; 10,25</t>
+          <t>5,74; 9,92</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,18; 8,7</t>
+          <t>5,44; 8,69</t>
         </is>
       </c>
     </row>
